--- a/assets/libreoffice_calc_njc/75911c73-370d-441e-9c04-b36e2d7efcc8/SalesProduct_L3_06.xlsx
+++ b/assets/libreoffice_calc_njc/75911c73-370d-441e-9c04-b36e2d7efcc8/SalesProduct_L3_06.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
   <si>
     <t xml:space="preserve">Month</t>
   </si>
@@ -60,16 +60,10 @@
     <t xml:space="preserve">Widget A</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">South</t>
   </si>
   <si>
     <t xml:space="preserve">Widget B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3</t>
   </si>
   <si>
     <t xml:space="preserve">Feb</t>
@@ -115,10 +109,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -140,6 +135,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,8 +187,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -207,428 +222,440 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AMJ1" s="0" t="n">
+      <c r="AMJ1" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="2" t="n">
         <f aca="false">F2-G2</f>
         <v>1200</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="2" t="n">
+        <f aca="false">H2/F2*100</f>
+        <v>40</v>
+      </c>
+      <c r="AMJ2" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AMJ2" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="2" t="n">
         <v>2550</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="2" t="n">
         <v>1700</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="2" t="n">
         <f aca="false">F3-G3</f>
         <v>850</v>
       </c>
-      <c r="I3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ3" s="0" t="n">
+      <c r="I3" s="3" t="n">
+        <f aca="false">H3/F3*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="AMJ3" s="2" t="n">
         <v>33.3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="2" t="n">
         <v>3750</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="2" t="n">
         <v>2250</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="2" t="n">
         <f aca="false">F4-G4</f>
         <v>1500</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="3" t="n">
+        <f aca="false">H4/F4*100</f>
+        <v>40</v>
+      </c>
+      <c r="AMJ4" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AMJ4" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="2" t="n">
         <v>2850</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="2" t="n">
         <v>1900</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="2" t="n">
         <f aca="false">F5-G5</f>
         <v>950</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="3" t="n">
+        <f aca="false">H5/F5*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="AMJ5" s="2" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AMJ5" s="0" t="n">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="2" t="n">
         <f aca="false">F6-G6</f>
         <v>2000</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="3" t="n">
+        <f aca="false">H6/F6*100</f>
+        <v>40</v>
+      </c>
+      <c r="AMJ6" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AMJ6" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <v>3300</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="2" t="n">
         <v>2200</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="2" t="n">
         <f aca="false">F7-G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ7" s="0" t="n">
+      <c r="I7" s="3" t="n">
+        <f aca="false">H7/F7*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="AMJ7" s="2" t="n">
         <v>33.3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="2" t="n">
         <v>2700</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="2" t="n">
         <f aca="false">F8-G8</f>
         <v>1800</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="3" t="n">
+        <f aca="false">H8/F8*100</f>
+        <v>40</v>
+      </c>
+      <c r="AMJ8" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AMJ8" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="0" t="s">
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>3900</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="2" t="n">
         <v>2600</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="2" t="n">
         <f aca="false">F9-G9</f>
         <v>1300</v>
       </c>
-      <c r="I9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ9" s="0" t="n">
+      <c r="I9" s="3" t="n">
+        <f aca="false">H9/F9*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="AMJ9" s="2" t="n">
         <v>33.3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="0" t="s">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>4000</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="2" t="n">
         <v>2400</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="2" t="n">
         <f aca="false">F10-G10</f>
         <v>1600</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="3" t="n">
+        <f aca="false">H10/F10*100</f>
+        <v>40</v>
+      </c>
+      <c r="AMJ10" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AMJ10" s="0" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="2" t="n">
         <f aca="false">F11-G11</f>
         <v>1000</v>
       </c>
-      <c r="I11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ11" s="0" t="n">
+      <c r="I11" s="3" t="n">
+        <f aca="false">H11/F11*100</f>
+        <v>33.3333333333333</v>
+      </c>
+      <c r="AMJ11" s="2" t="n">
         <v>33.3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="0" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>5250</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="2" t="n">
         <v>3150</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="2" t="n">
         <f aca="false">F12-G12</f>
         <v>2100</v>
       </c>
-      <c r="I12" s="0" t="s">
+      <c r="I12" s="3" t="n">
+        <f aca="false">H12/F12*100</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>4200</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="2" t="n">
         <v>2800</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="2" t="n">
         <f aca="false">F13-G13</f>
         <v>1400</v>
       </c>
-      <c r="I13" s="0" t="s">
-        <v>15</v>
+      <c r="I13" s="3" t="n">
+        <f aca="false">H13/F13*100</f>
+        <v>33.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -648,57 +675,57 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="0" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>25500</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10200</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="0" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>19800</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>1020</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>25500</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>10200</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>660</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>6600</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -718,103 +745,103 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>21</v>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>150</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>95</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B5" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>110</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B6" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>180</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>130</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>160</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>350</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/75911c73-370d-441e-9c04-b36e2d7efcc8/SalesProduct_L3_06.xlsx
+++ b/assets/libreoffice_calc_njc/75911c73-370d-441e-9c04-b36e2d7efcc8/SalesProduct_L3_06.xlsx
@@ -192,11 +192,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -224,7 +224,7 @@
   <dimension ref="A1:AMJ13"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -252,67 +252,67 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AMJ1" s="1" t="n">
+      <c r="AMJ1" s="2" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>1800</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <f aca="false">F2-G2</f>
         <v>1200</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <f aca="false">H2/F2*100</f>
         <v>40</v>
       </c>
-      <c r="AMJ2" s="2" t="n">
+      <c r="AMJ2" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>2550</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>1700</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <f aca="false">F3-G3</f>
         <v>850</v>
       </c>
@@ -320,33 +320,33 @@
         <f aca="false">H3/F3*100</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="AMJ3" s="2" t="n">
+      <c r="AMJ3" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>3750</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <f aca="false">F4-G4</f>
         <v>1500</v>
       </c>
@@ -354,33 +354,33 @@
         <f aca="false">H4/F4*100</f>
         <v>40</v>
       </c>
-      <c r="AMJ4" s="2" t="n">
+      <c r="AMJ4" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>2850</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">F5-G5</f>
         <v>950</v>
       </c>
@@ -388,33 +388,33 @@
         <f aca="false">H5/F5*100</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="AMJ5" s="2" t="n">
+      <c r="AMJ5" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">F6-G6</f>
         <v>2000</v>
       </c>
@@ -422,33 +422,33 @@
         <f aca="false">H6/F6*100</f>
         <v>40</v>
       </c>
-      <c r="AMJ6" s="2" t="n">
+      <c r="AMJ6" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>3300</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>2200</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <f aca="false">F7-G7</f>
         <v>1100</v>
       </c>
@@ -456,33 +456,33 @@
         <f aca="false">H7/F7*100</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="AMJ7" s="2" t="n">
+      <c r="AMJ7" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>4500</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="1" t="n">
         <v>2700</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <f aca="false">F8-G8</f>
         <v>1800</v>
       </c>
@@ -490,33 +490,33 @@
         <f aca="false">H8/F8*100</f>
         <v>40</v>
       </c>
-      <c r="AMJ8" s="2" t="n">
+      <c r="AMJ8" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>3900</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="1" t="n">
         <v>2600</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">F9-G9</f>
         <v>1300</v>
       </c>
@@ -524,33 +524,33 @@
         <f aca="false">H9/F9*100</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="AMJ9" s="2" t="n">
+      <c r="AMJ9" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="1" t="n">
         <v>2400</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <f aca="false">F10-G10</f>
         <v>1600</v>
       </c>
@@ -558,33 +558,33 @@
         <f aca="false">H10/F10*100</f>
         <v>40</v>
       </c>
-      <c r="AMJ10" s="2" t="n">
+      <c r="AMJ10" s="1" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="1" t="n">
         <v>3000</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <f aca="false">F11-G11</f>
         <v>1000</v>
       </c>
@@ -592,33 +592,33 @@
         <f aca="false">H11/F11*100</f>
         <v>33.3333333333333</v>
       </c>
-      <c r="AMJ11" s="2" t="n">
+      <c r="AMJ11" s="1" t="n">
         <v>33.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="1" t="n">
         <v>5250</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="1" t="n">
         <v>3150</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <f aca="false">F12-G12</f>
         <v>2100</v>
       </c>
@@ -628,28 +628,28 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="1" t="n">
         <v>4200</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="1" t="n">
         <v>2800</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <f aca="false">F13-G13</f>
         <v>1400</v>
       </c>
@@ -675,56 +675,56 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>1020</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>25500</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>10200</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>660</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>19800</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>6600</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
@@ -745,103 +745,103 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>210</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>350</v>
       </c>
     </row>
